--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
@@ -94,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{data2.skuName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{data2.warehouseName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,6 +131,10 @@
   </si>
   <si>
     <t>{data1.approveTime}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{data2.productName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,37 +565,37 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
@@ -78,63 +78,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{data1.code}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.sourceCode}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.billTypeName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.skuNo}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.warehouseName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.warehouseLocation}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.usableQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.frozenQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.qty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.diffQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.stocktakingUserName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.createTime}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.approveUserName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data1.approveTime}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{data2.productName}</t>
+    <t>{.code}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.billTypeName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.warehouseLocation}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.usableQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.frozenQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.qty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.diffQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.stocktakingUserName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,37 +565,37 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>单据编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,15 +126,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{.approveTime}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{.createTime}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.approveUserName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.approveTime}</t>
+    <t>{.createUserName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -484,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -500,11 +508,11 @@
     <col min="11" max="11" width="16.875" customWidth="1"/>
     <col min="12" max="12" width="17.75" customWidth="1"/>
     <col min="13" max="13" width="18.5" customWidth="1"/>
-    <col min="14" max="14" width="23.25" customWidth="1"/>
-    <col min="15" max="15" width="27.5" customWidth="1"/>
+    <col min="14" max="15" width="23.25" customWidth="1"/>
+    <col min="16" max="16" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,10 +556,13 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -589,13 +600,16 @@
         <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingProfitLoss.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>单据编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -142,7 +142,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>创建时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{.createUserName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.createTime}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" customWidth="1"/>
@@ -504,15 +512,17 @@
     <col min="7" max="7" width="26.5" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="19.375" customWidth="1"/>
-    <col min="11" max="11" width="16.875" customWidth="1"/>
-    <col min="12" max="12" width="17.75" customWidth="1"/>
-    <col min="13" max="13" width="18.5" customWidth="1"/>
-    <col min="14" max="15" width="23.25" customWidth="1"/>
-    <col min="16" max="16" width="27.5" customWidth="1"/>
+    <col min="10" max="10" width="21.375" customWidth="1"/>
+    <col min="11" max="11" width="19.875" customWidth="1"/>
+    <col min="12" max="12" width="30.625" customWidth="1"/>
+    <col min="13" max="13" width="20.625" customWidth="1"/>
+    <col min="14" max="14" width="23.25" customWidth="1"/>
+    <col min="15" max="15" width="27.5" customWidth="1"/>
+    <col min="16" max="16" width="24.375" customWidth="1"/>
+    <col min="17" max="17" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,13 +566,16 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
+      <c r="Q1" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -606,10 +619,13 @@
         <v>29</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
